--- a/out/MLP-S4_repeat_4_000007.xlsx
+++ b/out/MLP-S4_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003538824241188122</v>
+        <v>-0.000232232566474122</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.079741699258714</v>
+        <v>2.677298505935268</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC40" t="n">
-        <v>8.165789942918613</v>
+        <v>5.358735632192009</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.6117754666161401</v>
+        <v>0.4014728537928884</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.329251253104851</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.304123602363333</v>
+        <v>3.480789530985163</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7649183921337491</v>
+        <v>0.5019716413191014</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.222282074225238</v>
+        <v>4.083323830095891</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.096506724898557</v>
+        <v>0.7195739672797878</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.729251253104852</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.650809134797279</v>
+        <v>5.020783620338048</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.173045347884962</v>
+        <v>0.7698019599924881</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.729251253104852</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC44" t="n">
-        <v>8.900474533913467</v>
+        <v>5.840866897859198</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.243191630517568</v>
+        <v>0.8158341790740898</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC45" t="n">
-        <v>10.21390121139299</v>
+        <v>6.702793023532682</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5610292610115669</v>
+        <v>0.3681714573627513</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC46" t="n">
-        <v>10.0917350155928</v>
+        <v>6.622622327503167</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2709514903614862</v>
+        <v>0.1778099860622798</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC47" t="n">
-        <v>10.07216881170255</v>
+        <v>6.609782145534156</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1291003184178782</v>
+        <v>0.08472055172286035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.729251253104852</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC48" t="n">
-        <v>10.0592027851292</v>
+        <v>6.601273283859056</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0382515238121213</v>
+        <v>0.02510247170336665</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC49" t="n">
-        <v>10.00646799810424</v>
+        <v>6.566666205051449</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02530195658258603</v>
+        <v>0.01660434894760745</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC50" t="n">
-        <v>10.01880041476487</v>
+        <v>6.574759324211309</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01294876912103231</v>
+        <v>0.008495388259521314</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC51" t="n">
-        <v>10.01937823811419</v>
+        <v>6.575136801249811</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006620850188763339</v>
+        <v>0.004343780433828263</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC52" t="n">
-        <v>10.01966447082322</v>
+        <v>6.575322932682628</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002485908262449208</v>
+        <v>0.00162987142111525</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC53" t="n">
-        <v>10.01801016729367</v>
+        <v>6.574235600425918</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001352959838567659</v>
+        <v>0.0008860064554392907</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC54" t="n">
-        <v>10.01822803378639</v>
+        <v>6.574376831174483</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006490627493095043</v>
+        <v>0.0004241541733014973</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC55" t="n">
-        <v>10.01817234077701</v>
+        <v>6.574338569661648</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003994055532658016</v>
+        <v>0.0002606678817074609</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC56" t="n">
-        <v>10.01832276784178</v>
+        <v>6.574435550574811</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0002070500464420031</v>
+        <v>0.000133964836260536</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC57" t="n">
-        <v>10.01833624289172</v>
+        <v>6.57444265801045</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.79065924708733e-05</v>
+        <v>6.193923976260691e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC58" t="n">
-        <v>10.01832487327649</v>
+        <v>6.574433484356102</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.02364652658983e-05</v>
+        <v>3.849097684393219e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC59" t="n">
-        <v>10.01834867423505</v>
+        <v>6.574447498068668</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.530589321855379e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC60" t="n">
-        <v>10.01833772649598</v>
+        <v>6.574438609162351</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>8.38179904731087e-06</v>
+        <v>3.234953259883613e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC61" t="n">
-        <v>10.01832916366254</v>
+        <v>6.574431280243659</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC62" t="n">
-        <v>10.01832523921573</v>
+        <v>6.574427025065489</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC63" t="n">
-        <v>10.01831922778914</v>
+        <v>6.574421302786458</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC64" t="n">
-        <v>10.01831413454701</v>
+        <v>6.57441623343109</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC65" t="n">
-        <v>10.01830976957304</v>
+        <v>6.574411868457121</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC66" t="n">
-        <v>10.0183108608195</v>
+        <v>6.574412959703578</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.329251253104851</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC67" t="n">
-        <v>10.01831017121236</v>
+        <v>6.574412270096442</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC68" t="n">
-        <v>10.01831020152476</v>
+        <v>6.574412300408844</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC69" t="n">
-        <v>10.01831001207225</v>
+        <v>6.574412110956334</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC70" t="n">
-        <v>10.01831006511896</v>
+        <v>6.574412164003037</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC71" t="n">
-        <v>10.01831011816566</v>
+        <v>6.57441221704974</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC72" t="n">
-        <v>10.01831008027516</v>
+        <v>6.574412179159237</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC73" t="n">
-        <v>10.01830995144745</v>
+        <v>6.57441205033153</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC74" t="n">
-        <v>10.01830980746354</v>
+        <v>6.574411906347623</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC75" t="n">
-        <v>10.01830964832343</v>
+        <v>6.574411747207515</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC76" t="n">
-        <v>10.01830970137014</v>
+        <v>6.574411800254217</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC77" t="n">
-        <v>10.01830964832343</v>
+        <v>6.574411747207515</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC78" t="n">
-        <v>10.01830964832343</v>
+        <v>6.574411747207515</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC79" t="n">
-        <v>10.01830946644902</v>
+        <v>6.574411565333105</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC80" t="n">
-        <v>10.01830963316723</v>
+        <v>6.574411732051314</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC81" t="n">
-        <v>10.01830983019784</v>
+        <v>6.574411929081924</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC82" t="n">
-        <v>10.01830967105773</v>
+        <v>6.574411769941817</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC83" t="n">
-        <v>10.01830970894824</v>
+        <v>6.574411807832317</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC84" t="n">
-        <v>10.01830990597885</v>
+        <v>6.574412004862928</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC85" t="n">
-        <v>10.01830988324455</v>
+        <v>6.574411982128627</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC86" t="n">
-        <v>10.01830973168254</v>
+        <v>6.574411830566619</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC87" t="n">
-        <v>10.01830965590153</v>
+        <v>6.574411754785615</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC88" t="n">
-        <v>10.01830975441684</v>
+        <v>6.574411853300921</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC89" t="n">
-        <v>10.01830976199494</v>
+        <v>6.574411860879021</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC90" t="n">
-        <v>10.01831002722845</v>
+        <v>6.574412126112534</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC91" t="n">
-        <v>10.01830973168254</v>
+        <v>6.574411830566619</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC92" t="n">
-        <v>10.01830997418175</v>
+        <v>6.574412073065831</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC93" t="n">
-        <v>10.01831005754086</v>
+        <v>6.574412156424936</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.329251253104851</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC94" t="n">
-        <v>10.01830989082264</v>
+        <v>6.574411989706728</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC95" t="n">
-        <v>10.01831008027516</v>
+        <v>6.574412179159237</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC96" t="n">
-        <v>10.01830973168254</v>
+        <v>6.574411830566619</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC97" t="n">
-        <v>10.01830952707383</v>
+        <v>6.574411625957908</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC98" t="n">
-        <v>10.01830964074533</v>
+        <v>6.574411739629414</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC99" t="n">
-        <v>10.01830965590153</v>
+        <v>6.574411754785615</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC100" t="n">
-        <v>10.01830942098042</v>
+        <v>6.574411519864503</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC101" t="n">
-        <v>10.01830948160522</v>
+        <v>6.574411580489306</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC102" t="n">
-        <v>10.01830935277752</v>
+        <v>6.574411451661599</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>3.329251253104851</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC103" t="n">
-        <v>10.01830948918333</v>
+        <v>6.574411588067407</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC104" t="n">
-        <v>10.01830966347963</v>
+        <v>6.574411762363715</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC105" t="n">
-        <v>10.01830980746354</v>
+        <v>6.574411906347623</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC106" t="n">
-        <v>10.01830964074533</v>
+        <v>6.574411739629414</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC107" t="n">
-        <v>10.01830963316723</v>
+        <v>6.574411732051314</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC108" t="n">
-        <v>10.01830934519942</v>
+        <v>6.574411444083498</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC109" t="n">
-        <v>10.01830936035562</v>
+        <v>6.5744114592397</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC110" t="n">
-        <v>10.01830958769863</v>
+        <v>6.574411686582711</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC111" t="n">
-        <v>10.01830957254243</v>
+        <v>6.57441167142651</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC112" t="n">
-        <v>10.01830967863584</v>
+        <v>6.574411777519916</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC113" t="n">
-        <v>10.01830940582422</v>
+        <v>6.574411504708302</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC114" t="n">
-        <v>10.01830950433953</v>
+        <v>6.574411603223607</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC115" t="n">
-        <v>10.01830965590153</v>
+        <v>6.574411754785615</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC116" t="n">
-        <v>10.01830967105773</v>
+        <v>6.574411769941817</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC117" t="n">
-        <v>10.01830964832343</v>
+        <v>6.574411747207515</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC118" t="n">
-        <v>10.01830973168254</v>
+        <v>6.574411830566619</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC119" t="n">
-        <v>10.01830983019784</v>
+        <v>6.574411929081924</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC120" t="n">
-        <v>10.01830966347963</v>
+        <v>6.574411762363715</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC121" t="n">
-        <v>10.01830964832343</v>
+        <v>6.574411747207515</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC122" t="n">
-        <v>10.01830961801103</v>
+        <v>6.574411716895113</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC123" t="n">
-        <v>10.01830960285483</v>
+        <v>6.574411701738913</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC124" t="n">
-        <v>10.01830964074533</v>
+        <v>6.574411739629414</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC125" t="n">
-        <v>10.01830965590153</v>
+        <v>6.574411754785615</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC126" t="n">
-        <v>10.01830964832343</v>
+        <v>6.574411747207515</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000007.xlsx
+++ b/out/MLP-S4_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962525</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962525</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003538824241188122</v>
+        <v>-0.0002706047195544233</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.079741699258714</v>
+        <v>3.119672683256986</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC40" t="n">
-        <v>8.165789942918613</v>
+        <v>6.244167969034315</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.6117754666161401</v>
+        <v>0.4678088350142237</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.304123602363333</v>
+        <v>4.055925819860486</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7649183921337491</v>
+        <v>0.5849133156594981</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.222282074225238</v>
+        <v>4.758017862097196</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.096506724898557</v>
+        <v>0.8384704641040128</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.729251253104852</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.650809134797279</v>
+        <v>5.850375567118492</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.173045347884962</v>
+        <v>0.8969969644821033</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC44" t="n">
-        <v>8.900474533913467</v>
+        <v>6.805962243481819</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.243191630517568</v>
+        <v>0.9506367219858297</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC45" t="n">
-        <v>10.21390121139299</v>
+        <v>7.810305902655311</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5610292610115669</v>
+        <v>0.4290046719540169</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC46" t="n">
-        <v>10.0917350155928</v>
+        <v>7.716888549238423</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2709514903614862</v>
+        <v>0.2071896482340246</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC47" t="n">
-        <v>10.07216881170255</v>
+        <v>7.70192677546893</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1291003184178782</v>
+        <v>0.09871908605947417</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.729251253104852</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC48" t="n">
-        <v>10.0592027851292</v>
+        <v>7.692011988770401</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0382515238121213</v>
+        <v>0.02925013978098177</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC49" t="n">
-        <v>10.00646799810424</v>
+        <v>7.651686800697461</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02530195658258603</v>
+        <v>0.01934787671225929</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC50" t="n">
-        <v>10.01880041476487</v>
+        <v>7.661117141641068</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01294876912103231</v>
+        <v>0.00990047616721855</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC51" t="n">
-        <v>10.01937823811419</v>
+        <v>7.661557814459727</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006620850188763339</v>
+        <v>0.005061530537837418</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC52" t="n">
-        <v>10.01966447082322</v>
+        <v>7.661775514161937</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002485908262449208</v>
+        <v>0.001900079336549576</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC53" t="n">
-        <v>10.01801016729367</v>
+        <v>7.660509296435021</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001352959838567659</v>
+        <v>0.001032857519391322</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC54" t="n">
-        <v>10.01822803378639</v>
+        <v>7.660674696380234</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006490627493095043</v>
+        <v>0.0004948851389011886</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC55" t="n">
-        <v>10.01817234077701</v>
+        <v>7.66063092256492</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003994055532658016</v>
+        <v>0.0003049458619920377</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC56" t="n">
-        <v>10.01832276784178</v>
+        <v>7.660744900296945</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0002070500464420031</v>
+        <v>0.0001566109577252159</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC57" t="n">
-        <v>10.01833624289172</v>
+        <v>7.66075402626477</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.79065924708733e-05</v>
+        <v>7.392835733202904e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC58" t="n">
-        <v>10.01832487327649</v>
+        <v>7.660744140831728</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.02364652658983e-05</v>
+        <v>4.488670873274575e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC59" t="n">
-        <v>10.01834867423505</v>
+        <v>7.660761231068211</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.530589321855379e-05</v>
+        <v>1.831222555273368e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC60" t="n">
-        <v>10.01833772649598</v>
+        <v>7.660751655884309</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>8.38179904731087e-06</v>
+        <v>5.293691574854516e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC61" t="n">
-        <v>10.01832916366254</v>
+        <v>7.660743915243203</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC62" t="n">
-        <v>10.01832523921573</v>
+        <v>7.66073974207161</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC63" t="n">
-        <v>10.01831922778914</v>
+        <v>7.660734019792579</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962523</v>
       </c>
       <c r="JC64" t="n">
-        <v>10.01831413454701</v>
+        <v>7.66072895043721</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534075</v>
       </c>
       <c r="JC65" t="n">
-        <v>10.01830976957304</v>
+        <v>7.660724585463242</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC66" t="n">
-        <v>10.0183108608195</v>
+        <v>7.660725676709698</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534075</v>
       </c>
       <c r="JC67" t="n">
-        <v>10.01831017121236</v>
+        <v>7.660724987102562</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC68" t="n">
-        <v>10.01831020152476</v>
+        <v>7.660725017414965</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC69" t="n">
-        <v>10.01831001207225</v>
+        <v>7.660724827962454</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC70" t="n">
-        <v>10.01831006511896</v>
+        <v>7.660724881009158</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC71" t="n">
-        <v>10.01831011816566</v>
+        <v>7.660724934055859</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC72" t="n">
-        <v>10.01831008027516</v>
+        <v>7.660724896165358</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC73" t="n">
-        <v>10.01830995144745</v>
+        <v>7.660724767337652</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC74" t="n">
-        <v>10.01830980746354</v>
+        <v>7.660724623353744</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC75" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC76" t="n">
-        <v>10.01830970137014</v>
+        <v>7.66072451726034</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC77" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC78" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC79" t="n">
-        <v>10.01830946644902</v>
+        <v>7.660724282339227</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC80" t="n">
-        <v>10.01830963316723</v>
+        <v>7.660724449057436</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC81" t="n">
-        <v>10.01830983019784</v>
+        <v>7.660724646088045</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC82" t="n">
-        <v>10.01830967105773</v>
+        <v>7.660724486947937</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC83" t="n">
-        <v>10.01830970894824</v>
+        <v>7.660724524838439</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC84" t="n">
-        <v>10.01830990597885</v>
+        <v>7.66072472186905</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC85" t="n">
-        <v>10.01830988324455</v>
+        <v>7.660724699134748</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC86" t="n">
-        <v>10.01830973168254</v>
+        <v>7.660724547572739</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC87" t="n">
-        <v>10.01830965590153</v>
+        <v>7.660724471791736</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC88" t="n">
-        <v>10.01830975441684</v>
+        <v>7.660724570307041</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC89" t="n">
-        <v>10.01830976199494</v>
+        <v>7.660724577885142</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC90" t="n">
-        <v>10.01831002722845</v>
+        <v>7.660724843118655</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC91" t="n">
-        <v>10.01830973168254</v>
+        <v>7.660724547572739</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC92" t="n">
-        <v>10.01830997418175</v>
+        <v>7.660724790071953</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC93" t="n">
-        <v>10.01831005754086</v>
+        <v>7.660724873431056</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC94" t="n">
-        <v>10.01830989082264</v>
+        <v>7.660724706712847</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC95" t="n">
-        <v>10.01831008027516</v>
+        <v>7.660724896165358</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC96" t="n">
-        <v>10.01830973168254</v>
+        <v>7.660724547572739</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC97" t="n">
-        <v>10.01830952707383</v>
+        <v>7.660724342964029</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC98" t="n">
-        <v>10.01830964074533</v>
+        <v>7.660724456635535</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC99" t="n">
-        <v>10.01830965590153</v>
+        <v>7.660724471791736</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC100" t="n">
-        <v>10.01830942098042</v>
+        <v>7.660724236870625</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC101" t="n">
-        <v>10.01830948160522</v>
+        <v>7.660724297495427</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC102" t="n">
-        <v>10.01830935277752</v>
+        <v>7.660724168667721</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC103" t="n">
-        <v>10.01830948918333</v>
+        <v>7.660724305073527</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962523</v>
       </c>
       <c r="JC104" t="n">
-        <v>10.01830966347963</v>
+        <v>7.660724479369836</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC105" t="n">
-        <v>10.01830980746354</v>
+        <v>7.660724623353744</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC106" t="n">
-        <v>10.01830964074533</v>
+        <v>7.660724456635535</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC107" t="n">
-        <v>10.01830963316723</v>
+        <v>7.660724449057436</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC108" t="n">
-        <v>10.01830934519942</v>
+        <v>7.66072416108962</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC109" t="n">
-        <v>10.01830936035562</v>
+        <v>7.66072417624582</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC110" t="n">
-        <v>10.01830958769863</v>
+        <v>7.660724403588834</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC111" t="n">
-        <v>10.01830957254243</v>
+        <v>7.660724388432631</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC112" t="n">
-        <v>10.01830967863584</v>
+        <v>7.660724494526038</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC113" t="n">
-        <v>10.01830940582422</v>
+        <v>7.660724221714422</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC114" t="n">
-        <v>10.01830950433953</v>
+        <v>7.660724320229728</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC115" t="n">
-        <v>10.01830965590153</v>
+        <v>7.660724471791736</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC116" t="n">
-        <v>10.01830967105773</v>
+        <v>7.660724486947937</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC117" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC118" t="n">
-        <v>10.01830973168254</v>
+        <v>7.660724547572739</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC119" t="n">
-        <v>10.01830983019784</v>
+        <v>7.660724646088045</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC120" t="n">
-        <v>10.01830966347963</v>
+        <v>7.660724479369836</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC121" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC122" t="n">
-        <v>10.01830961801103</v>
+        <v>7.660724433901233</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC123" t="n">
-        <v>10.01830960285483</v>
+        <v>7.660724418745033</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC124" t="n">
-        <v>10.01830964074533</v>
+        <v>7.660724456635535</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC125" t="n">
-        <v>10.01830965590153</v>
+        <v>7.660724471791736</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC126" t="n">
-        <v>10.01830964832343</v>
+        <v>7.660724464213636</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000007.xlsx
+++ b/out/MLP-S4_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4003371298313141</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4115478694438934</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3996768593788147</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.3566176397962524</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5552659630775452</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5566176397962525</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4698548316955566</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4212284684181213</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.395575076341629</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4133364856243134</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4161064028739929</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4253395199775696</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4103443026542664</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3992386162281036</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.435581237077713</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4304592907428741</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4605050683021545</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4402906596660614</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4435228407382965</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.422693133354187</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4594140350818634</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4682212471961975</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5566176397962526</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.5055843591690063</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.396909249534076</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5732345581054688</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.5011053085327148</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.396909249534076</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4751865565776825</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5566176397962526</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4635246098041534</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4527906477451324</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.443383663892746</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4933472275733948</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.480724960565567</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4679064452648163</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4582464396953583</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4505859911441803</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4579869508743286</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.464554637670517</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5566176397962525</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5550839304924011</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.396909249534076</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.7504538893699646</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.237200859271899</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.620473325252533</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.581864595413208</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.237200859271899</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002706047195544233</v>
+        <v>-0.0001655819800505415</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.119672683256986</v>
+        <v>1.908915605419707</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5761157870292664</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.237200859271899</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.244167969034315</v>
+        <v>3.820782201421234</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4678088350142237</v>
+        <v>0.2862504102768729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5508442521095276</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.396909249534076</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.055925819860486</v>
+        <v>2.481805283148065</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5849133156594981</v>
+        <v>0.3579062094468367</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4959213137626648</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.396909249534076</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.758017862097196</v>
+        <v>2.911412704952789</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8384704641040128</v>
+        <v>0.5130568539070393</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6250072121620178</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.196909249534075</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.850375567118492</v>
+        <v>3.579822185635244</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8969969644821033</v>
+        <v>0.5488688594293036</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6796943545341492</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.037200859271898</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.805962243481819</v>
+        <v>4.164541999836108</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9506367219858297</v>
+        <v>0.5816910990992846</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7327226996421814</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.237200859271899</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.810305902655311</v>
+        <v>4.779096175439199</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4290046719540169</v>
+        <v>0.2625057084191442</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.8063890933990479</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.396909249534076</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.716888549238423</v>
+        <v>4.721934442921425</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2071896482340246</v>
+        <v>0.1267789021009197</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.4820665717124939</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.196909249534075</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.70192677546893</v>
+        <v>4.712779365589396</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09871908605947417</v>
+        <v>0.06040575950735491</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5993105173110962</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3566176397962524</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.692011988770401</v>
+        <v>4.706712529200177</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02925013978098177</v>
+        <v>0.01789816837695915</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4200620353221893</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3566176397962524</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.651686800697461</v>
+        <v>4.682037535803007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01934787671225929</v>
+        <v>0.01183757656008916</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4349517524242401</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.661117141641068</v>
+        <v>4.687806569566344</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00990047616721855</v>
+        <v>0.006056163523399848</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3484014868736267</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.661557814459727</v>
+        <v>4.688074276883612</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005061530537837418</v>
+        <v>0.003095519383377557</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.424231082201004</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.661775514161937</v>
+        <v>4.68820554651627</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001900079336549576</v>
+        <v>0.001160602772461799</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4000627100467682</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.660509296435021</v>
+        <v>4.687428883703615</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001032857519391322</v>
+        <v>0.0006302546024891238</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3827163875102997</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.660674696380234</v>
+        <v>4.687528140811389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004948851389011886</v>
+        <v>0.0003009710309649564</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.3977179527282715</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.66063092256492</v>
+        <v>4.687499426584645</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003049458619920377</v>
+        <v>0.0001839193825475277</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4253612160682678</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.660744900296945</v>
+        <v>4.687567135797627</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001566109577252159</v>
+        <v>9.381943911860337e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3392331898212433</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.66075402626477</v>
+        <v>4.68757079099824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.392835733202904e-05</v>
+        <v>4.295647027768853e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7685793042182922</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.396909249534076</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.660744140831728</v>
+        <v>4.687562792321457</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.488670873274575e-05</v>
+        <v>2.569951306630508e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5640922784805298</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.396909249534076</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.660761231068211</v>
+        <v>4.687571494155336</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3637519776821136</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.660751655884309</v>
+        <v>4.687563635373489</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3569116294384003</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.660743915243203</v>
+        <v>4.687556854583018</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3529409170150757</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.66073974207161</v>
+        <v>4.687552434039168</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3783730268478394</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.660734019792579</v>
+        <v>4.687546855744045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4479727149009705</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3566176397962523</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.66072895043721</v>
+        <v>4.687541809122977</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6977955102920532</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.396909249534075</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.660724585463242</v>
+        <v>4.687542127403193</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.9389397501945496</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.237200859271899</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.660725676709698</v>
+        <v>4.68754321864965</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.7333800196647644</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.396909249534075</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.660724987102562</v>
+        <v>4.687542529042514</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4238274395465851</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.660725017414965</v>
+        <v>4.687542559354916</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.309867799282074</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.660724827962454</v>
+        <v>4.687542369902406</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.2963490188121796</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.660724881009158</v>
+        <v>4.687542422949109</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2224642485380173</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.660724934055859</v>
+        <v>4.687542475995811</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2159671187400818</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.660724896165358</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2800372838973999</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.660724767337652</v>
+        <v>4.687542309277602</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.2759716510772705</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.660724623353744</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2885694205760956</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.326055109500885</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.66072451726034</v>
+        <v>4.68754205920029</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2803807854652405</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3450455367565155</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3908323347568512</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.660724282339227</v>
+        <v>4.687541824279178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4106267690658569</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.660724449057436</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3860381841659546</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.660724646088045</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3125472068786621</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.660724486947937</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.3873327076435089</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.660724524838439</v>
+        <v>4.68754206677839</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4810916185379028</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.66072472186905</v>
+        <v>4.687542263809</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3615042865276337</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.660724699134748</v>
+        <v>4.687542241074699</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3008914589881897</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.660724547572739</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3143969774246216</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.660724471791736</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.3700059652328491</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.660724570307041</v>
+        <v>4.687542112246993</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.4776674211025238</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.660724577885142</v>
+        <v>4.687542119825094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3972135782241821</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.660724843118655</v>
+        <v>4.687542385058607</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3237724602222443</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.660724547572739</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4411543011665344</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.660724790071953</v>
+        <v>4.687542332011904</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3304681181907654</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.660724873431056</v>
+        <v>4.687542415371008</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.5189040303230286</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.660724706712847</v>
+        <v>4.6875422486528</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.388227790594101</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.660724896165358</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3431916534900665</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.660724547572739</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2815587818622589</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.660724342964029</v>
+        <v>4.687541884903981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.2672758102416992</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.660724456635535</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3459223508834839</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.660724471791736</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3872251212596893</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.660724236870625</v>
+        <v>4.687541778810576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3506644070148468</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.660724297495427</v>
+        <v>4.687541839435378</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3333377838134766</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3566176397962524</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.660724168667721</v>
+        <v>4.687541710607671</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5171555280685425</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.660724305073527</v>
+        <v>4.687541847013479</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4340506196022034</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.5566176397962523</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.660724479369836</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3881275057792664</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.2836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.660724623353744</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3968986570835114</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.2836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.660724456635535</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3965941965579987</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.660724449057436</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.2939068078994751</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.66072416108962</v>
+        <v>4.687541703029571</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3347824513912201</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.66072417624582</v>
+        <v>4.687541718185773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.342649519443512</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.660724403588834</v>
+        <v>4.687541945528784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3773620128631592</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.660724388432631</v>
+        <v>4.687541930372583</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.343035489320755</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.660724494526038</v>
+        <v>4.687542036465988</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3140927851200104</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.660724221714422</v>
+        <v>4.687541763654375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3492786884307861</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.660724320229728</v>
+        <v>4.687541862169679</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3494595885276794</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.660724471791736</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.317502498626709</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.660724486947937</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3716893196105957</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4211559891700745</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.660724547572739</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3529816269874573</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.660724646088045</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3325679004192352</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.660724479369836</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3379879295825958</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3277383148670197</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.660724433901233</v>
+        <v>4.687541975841185</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3275358974933624</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.660724418745033</v>
+        <v>4.687541960684985</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3066935241222382</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.660724456635535</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3568638861179352</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3700000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.660724471791736</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.429880678653717</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.660724464213636</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000007.xlsx
+++ b/out/MLP-S4_repeat_4_000007.xlsx
@@ -70904,7 +70904,7 @@
         <v>0.3700059652328491</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>4.687542112246993</v>
@@ -71699,7 +71699,7 @@
         <v>0.4776674211025238</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>4.687542119825094</v>
@@ -72494,7 +72494,7 @@
         <v>0.3972135782241821</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC90" t="n">
         <v>4.687542385058607</v>
@@ -73289,7 +73289,7 @@
         <v>0.3237724602222443</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC91" t="n">
         <v>4.687542089512691</v>
@@ -74084,7 +74084,7 @@
         <v>0.4411543011665344</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>4.687542332011904</v>
@@ -77264,7 +77264,7 @@
         <v>0.3431916534900665</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5799999999999998</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
         <v>4.687542089512691</v>
@@ -81239,7 +81239,7 @@
         <v>0.3506644070148468</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
         <v>4.687541839435378</v>
